--- a/astro-site/public/dl/plan-negocio-cocteleria-eventos/plan-financiero-cocteleria-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-cocteleria-eventos/plan-financiero-cocteleria-eventos.xlsx
@@ -14,7 +14,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personal Freelance" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Inversion Inicial'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'PyG 3 Anos'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Punto Equilibrio'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Escenarios'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Personal Freelance'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -541,7 +547,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -572,6 +578,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -968,7 +975,16 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -976,7 +992,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1002,6 +1018,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1627,7 +1644,16 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1635,7 +1661,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1659,6 +1685,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1851,6 +1878,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
@@ -1867,10 +1895,19 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A18:C18"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1878,7 +1915,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1903,6 +1940,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2111,7 +2149,16 @@
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2119,7 +2166,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2146,6 +2193,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2342,6 +2390,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
@@ -2399,13 +2448,22 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A14:E14"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2413,9 +2471,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2430,6 +2488,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2479,6 +2538,8 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
@@ -2823,6 +2884,14 @@
       <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Modelo escalable sin coste estructura fijo</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/plan-negocio-cocteleria-eventos · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -2830,6 +2899,15 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>